--- a/anova.xlsx
+++ b/anova.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Työpöytä/Probability/2_Statistics/Statistics25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lucit-my.sharepoint.com/personal/jouko_teeriaho_lapinamk_fi/Documents/Tiedostot/GitHub/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{CE84167A-F2B7-428A-AF11-D625853B0330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F151404D-80EF-49B8-9A76-6D52802F53BA}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{48F666FD-7E32-4682-ABFC-8FB9E62B027E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D072B0-9B15-4CD0-8AAA-7524A1C0B51B}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="0" windowWidth="19110" windowHeight="10000" xr2:uid="{15275900-D5A1-42FE-B017-D9F4E6910AF5}"/>
+    <workbookView xWindow="1520" yWindow="840" windowWidth="16150" windowHeight="9960" xr2:uid="{15275900-D5A1-42FE-B017-D9F4E6910AF5}"/>
   </bookViews>
   <sheets>
     <sheet name="OneWay Anova" sheetId="1" r:id="rId1"/>
@@ -181,32 +181,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -215,9 +200,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -226,6 +208,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -247,10 +232,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,39 +564,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -623,17 +604,16 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="6">
         <v>91</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
         <v>97</v>
       </c>
-      <c r="D7" s="1">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),65,10),0)</f>
-        <v>62</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="6">
+        <v>58</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -641,17 +621,16 @@
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="6">
         <v>80</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>96</v>
       </c>
-      <c r="D8" s="1">
-        <f t="shared" ref="D8:D20" ca="1" si="0">ROUND(_xlfn.NORM.INV(RAND(),65,10),0)</f>
-        <v>63</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="D8" s="6">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -659,189 +638,180 @@
       <c r="A9">
         <v>3</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="6">
         <v>69</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="6">
         <v>88</v>
       </c>
-      <c r="D9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+      <c r="D9" s="6">
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="6">
         <v>71</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="6">
         <v>72</v>
       </c>
-      <c r="D10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+      <c r="D10" s="6">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="6">
         <v>85</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="6">
         <v>64</v>
       </c>
-      <c r="D11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+      <c r="D11" s="6">
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="6">
         <v>71</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
         <v>66</v>
       </c>
-      <c r="D12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+      <c r="D12" s="6">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>7</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="6">
         <v>79</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="6">
         <v>83</v>
       </c>
-      <c r="D13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+      <c r="D13" s="6">
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="6">
         <v>72</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="6">
         <v>72</v>
       </c>
-      <c r="D14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+      <c r="D14" s="6">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>9</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <v>78</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="6">
         <v>64</v>
       </c>
-      <c r="D15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+      <c r="D15" s="6">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>88</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="6">
         <v>74</v>
       </c>
-      <c r="D16" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+      <c r="D16" s="6">
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>11</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <v>89</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
         <v>52</v>
       </c>
-      <c r="D17" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+      <c r="D17" s="6">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>12</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <v>64</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="6">
         <v>58</v>
       </c>
-      <c r="D18" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+      <c r="D18" s="6">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>13</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="6">
         <v>69</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="6">
         <v>74</v>
       </c>
-      <c r="D19" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+      <c r="D19" s="6">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="6">
         <v>89</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>83</v>
       </c>
-      <c r="D20" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+      <c r="D20" s="6">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;10&amp;K000000 Luottamuksellinen - Confidential (3Y)&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" enabled="0" method="" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="1"/>
+  <clbl:label id="{d823ee79-bdbf-4d11-a783-980929fd6733}" enabled="1" method="Standard" siteId="{4c60a66f-0a8d-446e-9ac0-836a00d84542}" removed="0"/>
 </clbl:labelList>
 </file>